--- a/develop/StructureDefinition-mii-lm-person.xlsx
+++ b/develop/StructureDefinition-mii-lm-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="274">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04</t>
+    <t>2026-05-12</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,7 +231,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: RIM Mapping</t>
+    <t>Mapping: Person LogicalModel FHIR Mapping</t>
   </si>
   <si>
     <t>Person</t>
@@ -264,9 +264,6 @@
 </t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Person.id</t>
   </si>
   <si>
@@ -333,6 +330,9 @@
     <t>Vollständiger Name einer Person.</t>
   </si>
   <si>
+    <t>Patient.name</t>
+  </si>
+  <si>
     <t>Person.Name.id</t>
   </si>
   <si>
@@ -362,43 +362,58 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Person.Name.Vorname</t>
   </si>
   <si>
     <t>Vollständiger Vorname einer Person.</t>
   </si>
   <si>
+    <t>Patient.name.given</t>
+  </si>
+  <si>
     <t>Person.Name.Nachname</t>
   </si>
   <si>
     <t>Nachname einer Person ohne Vor- und Zusätze. Dient z.B. der alphabetischen Einordnung des Namens.</t>
   </si>
   <si>
+    <t>Patient.name.family.extension.nachname</t>
+  </si>
+  <si>
     <t>Person.Name.Familienname</t>
   </si>
   <si>
     <t>Der vollständige Familienname, einschließlich aller Vorsatz- und Zusatzwörter, mit Leerzeichen getrennt.</t>
   </si>
   <si>
+    <t>Patient.name.family</t>
+  </si>
+  <si>
     <t>Person.Name.Vorsatzwort</t>
   </si>
   <si>
     <t>Vorsatzwort wie z.B.: von, van, zu Vgl. auch VSDM-Spezifikation der Gematik (Versichertenstammdatenmanagement, "eGK")</t>
   </si>
   <si>
+    <t>Patient.name.family.extension.vorsatzwort</t>
+  </si>
+  <si>
     <t>Person.Name.Namenszusatz</t>
   </si>
   <si>
     <t>Namenszusatz als Bestandteil das Nachnamens, wie in VSDM (Versichertenstammdatenmanagement, "eGK") definiert. Beispiele: Gräfin, Prinz oder Fürst</t>
   </si>
   <si>
+    <t>Patient.name.family.extension.namenszusatz</t>
+  </si>
+  <si>
     <t>Person.Name.Praefix</t>
   </si>
   <si>
     <t>Namensteile vor dem Vornamen, z.B. akademischer Grad</t>
+  </si>
+  <si>
+    <t>Patient.name.prefix</t>
   </si>
   <si>
     <t>Person.Name.Praefix.id</t>
@@ -441,12 +456,18 @@
     <t>Art des Präfixes, z.B. "AC" für Akademische Titel</t>
   </si>
   <si>
+    <t>Patient.name.prefix.extension-prefix-qualifier</t>
+  </si>
+  <si>
     <t>Person.Name.Geburtsname</t>
   </si>
   <si>
     <t>Familienname einer Person zum Zeitpunkt ihrer Geburt. Kann sich danach z.B. durch Heirat und Annahme eines anderen Familiennamens ändern.</t>
   </si>
   <si>
+    <t>Patient.name.use</t>
+  </si>
+  <si>
     <t>Person.Demographie</t>
   </si>
   <si>
@@ -466,6 +487,9 @@
   </si>
   <si>
     <t>Administratives Geschlecht der Person</t>
+  </si>
+  <si>
+    <t>Patient.gender</t>
   </si>
   <si>
     <t>Person.Demographie.Geburtsdatum</t>
@@ -478,12 +502,18 @@
     <t>Geburtsdatum des Person.</t>
   </si>
   <si>
+    <t>Patient.birthDate</t>
+  </si>
+  <si>
     <t>Person.Demographie.Adresse</t>
   </si>
   <si>
     <t>Vollständige Anschrift einer Person für die postlische Kommunikation.</t>
   </si>
   <si>
+    <t>Patient.address</t>
+  </si>
+  <si>
     <t>Person.Demographie.Adresse.id</t>
   </si>
   <si>
@@ -514,22 +544,34 @@
     <t>Ländercode nach ISO 3166.</t>
   </si>
   <si>
+    <t>Patient.address.country</t>
+  </si>
+  <si>
     <t>Person.Demographie.Adresse.Strassenanschrift.PLZ</t>
   </si>
   <si>
     <t>Postleitzahl gemäß der im jeweiligen Land gültigen Konventionen.</t>
   </si>
   <si>
+    <t>Patient.address.postalCode</t>
+  </si>
+  <si>
     <t>Person.Demographie.Adresse.Strassenanschrift.Wohnort</t>
   </si>
   <si>
     <t>Bei Personen aus Stadtstaaten inklusive des Stadtteils.</t>
   </si>
   <si>
+    <t>Patient.address.city + Patient.address.extension.Stadtteil</t>
+  </si>
+  <si>
     <t>Person.Demographie.Adresse.Strassenanschrift.Strasse</t>
   </si>
   <si>
     <t>Straßenname mit Hausnummer oder Postfach sowie weitere Angaben zur Zustellung.</t>
+  </si>
+  <si>
+    <t>Patient.address.line</t>
   </si>
   <si>
     <t>Person.Demographie.Adresse.Postfach</t>
@@ -584,6 +626,9 @@
     <t>Gibt an, ob der Patient am Leben oder verstorben ist.</t>
   </si>
   <si>
+    <t>Patient.deceased[x]</t>
+  </si>
+  <si>
     <t>Person.Demographie.Vitalstatus.Todeszeitpunkt</t>
   </si>
   <si>
@@ -656,6 +701,9 @@
     <t>Gesundheitseinrichtungs-eigene Identifikationsnummer für einen Patienten</t>
   </si>
   <si>
+    <t>Patient.identifier:pid</t>
+  </si>
+  <si>
     <t>Person.PatientIn.PatientenIdentifikator.PatientenIdentifikatorKontext</t>
   </si>
   <si>
@@ -668,6 +716,9 @@
     <t>Aktuell gültige Versicherung der Patient:in welcher zur Abrechnung der Behandlungsleistung verwendet wird.</t>
   </si>
   <si>
+    <t>Patient.identifier:default</t>
+  </si>
+  <si>
     <t>Person.PatientIn.Versicherung.id</t>
   </si>
   <si>
@@ -713,10 +764,16 @@
     <t>Unveränderlicher Teil der Krankenversichertennummer (VersichertenID) bei GKV Patienten. Diese findet sich z.B. auf der Mitgliedskarte der Krankenkasse.</t>
   </si>
   <si>
+    <t>Patient.identifier:versichertenId_GKV</t>
+  </si>
+  <si>
     <t>Person.PatientIn.Versicherung.Versichertennummer.VersichertennummerPKV</t>
   </si>
   <si>
     <t>Versichertennummer bei PKV Patienten. Vergabe erfolgt durch die jeweilige Private Krankenversicherung.</t>
+  </si>
+  <si>
+    <t>Patient.identifier:versicherungsnummer_pkv</t>
   </si>
   <si>
     <t>Person.ProbandIn</t>
@@ -793,6 +850,9 @@
   </si>
   <si>
     <t>Neu generierte Identifikation der PatientIn mit Bezug zum Original-Identifikator in einer Treuhandstelle.</t>
+  </si>
+  <si>
+    <t>Patient.identifier:PseudonymisierterIdentifier</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1192,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="46.3984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1348,15 +1408,15 @@
         <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1367,25 +1427,25 @@
         <v>75</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1436,13 +1496,13 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>74</v>
@@ -1451,19 +1511,19 @@
         <v>74</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1482,16 +1542,16 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M4" t="s" s="2">
+      <c r="N4" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1529,19 +1589,19 @@
         <v>74</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -1553,18 +1613,18 @@
         <v>74</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1587,13 +1647,13 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1644,7 +1704,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -1659,7 +1719,7 @@
         <v>81</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>74</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
@@ -1678,25 +1738,25 @@
         <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1747,13 +1807,13 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>74</v>
@@ -1762,7 +1822,7 @@
         <v>74</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -1774,7 +1834,7 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1793,16 +1853,16 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1840,19 +1900,19 @@
         <v>74</v>
       </c>
       <c r="AB7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC7" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC7" t="s" s="2">
+      <c r="AD7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE7" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE7" t="s" s="2">
+      <c r="AF7" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -1864,10 +1924,10 @@
         <v>74</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -1898,7 +1958,7 @@
         <v>107</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>108</v>
@@ -1907,7 +1967,7 @@
         <v>109</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O8" t="s" s="2">
         <v>110</v>
@@ -1971,18 +2031,18 @@
         <v>74</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2005,13 +2065,13 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2062,7 +2122,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -2077,7 +2137,7 @@
         <v>74</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -2096,19 +2156,19 @@
         <v>75</v>
       </c>
       <c r="G10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K10" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="H10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K10" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>116</v>
@@ -2171,7 +2231,7 @@
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>74</v>
@@ -2180,15 +2240,15 @@
         <v>74</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2199,25 +2259,25 @@
         <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2268,13 +2328,13 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>74</v>
@@ -2283,15 +2343,15 @@
         <v>74</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>74</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2302,25 +2362,25 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L12" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2371,13 +2431,13 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>74</v>
@@ -2386,15 +2446,15 @@
         <v>74</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>74</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2405,25 +2465,25 @@
         <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K13" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K13" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L13" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2474,13 +2534,13 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>74</v>
@@ -2489,15 +2549,15 @@
         <v>74</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2520,13 +2580,13 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2577,7 +2637,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2592,15 +2652,15 @@
         <v>81</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>74</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2611,25 +2671,25 @@
         <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K15" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2680,13 +2740,13 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>74</v>
@@ -2700,14 +2760,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2726,16 +2786,16 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2785,7 +2845,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2797,7 +2857,7 @@
         <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>74</v>
@@ -2805,10 +2865,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2819,25 +2879,25 @@
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2861,7 +2921,7 @@
         <v>74</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="X17" t="s" s="2">
         <v>74</v>
@@ -2888,13 +2948,13 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
@@ -2908,10 +2968,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2922,7 +2982,7 @@
         <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>74</v>
@@ -2934,13 +2994,13 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2991,13 +3051,13 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>74</v>
@@ -3006,15 +3066,15 @@
         <v>74</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>74</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3025,25 +3085,25 @@
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K19" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3094,13 +3154,13 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -3109,15 +3169,15 @@
         <v>74</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>74</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3140,13 +3200,13 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3197,7 +3257,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3217,10 +3277,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3231,25 +3291,25 @@
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K21" t="s" s="2">
+      <c r="L21" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3300,13 +3360,13 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>74</v>
@@ -3315,19 +3375,19 @@
         <v>74</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3346,16 +3406,16 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3393,19 +3453,19 @@
         <v>74</v>
       </c>
       <c r="AB22" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC22" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC22" t="s" s="2">
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE22" t="s" s="2">
+      <c r="AF22" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3417,18 +3477,18 @@
         <v>74</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3451,7 +3511,7 @@
         <v>107</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>108</v>
@@ -3460,7 +3520,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O23" t="s" s="2">
         <v>110</v>
@@ -3524,18 +3584,18 @@
         <v>74</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3546,7 +3606,7 @@
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3558,13 +3618,13 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3615,13 +3675,13 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>74</v>
@@ -3630,15 +3690,15 @@
         <v>74</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>74</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3649,7 +3709,7 @@
         <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3661,13 +3721,13 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3718,13 +3778,13 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>74</v>
@@ -3733,15 +3793,15 @@
         <v>74</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>74</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3764,13 +3824,13 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3821,7 +3881,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3836,15 +3896,15 @@
         <v>81</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>74</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3855,25 +3915,25 @@
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K27" t="s" s="2">
+      <c r="L27" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3924,13 +3984,13 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>74</v>
@@ -3939,19 +3999,19 @@
         <v>74</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -3970,16 +4030,16 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4017,19 +4077,19 @@
         <v>74</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC28" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC28" t="s" s="2">
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE28" t="s" s="2">
+      <c r="AF28" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4041,18 +4101,18 @@
         <v>74</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4075,7 +4135,7 @@
         <v>107</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>108</v>
@@ -4084,7 +4144,7 @@
         <v>109</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>110</v>
@@ -4148,18 +4208,18 @@
         <v>74</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4182,13 +4242,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4239,7 +4299,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4259,10 +4319,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4273,25 +4333,25 @@
         <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K31" t="s" s="2">
+      <c r="L31" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4342,13 +4402,13 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>74</v>
@@ -4357,19 +4417,19 @@
         <v>74</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4388,16 +4448,16 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4435,19 +4495,19 @@
         <v>74</v>
       </c>
       <c r="AB32" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC32" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC32" t="s" s="2">
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE32" t="s" s="2">
+      <c r="AF32" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4459,18 +4519,18 @@
         <v>74</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4493,7 +4553,7 @@
         <v>107</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>108</v>
@@ -4502,7 +4562,7 @@
         <v>109</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O33" t="s" s="2">
         <v>110</v>
@@ -4566,18 +4626,18 @@
         <v>74</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4585,28 +4645,28 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K34" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L34" t="s" s="2">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4657,13 +4717,13 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>74</v>
@@ -4672,15 +4732,15 @@
         <v>74</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>74</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4688,28 +4748,28 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L35" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4760,13 +4820,13 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>74</v>
@@ -4775,15 +4835,15 @@
         <v>74</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>74</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4791,28 +4851,28 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L36" t="s" s="2">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4863,13 +4923,13 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>74</v>
@@ -4878,15 +4938,15 @@
         <v>74</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>74</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4894,28 +4954,28 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L37" t="s" s="2">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4966,13 +5026,13 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>74</v>
@@ -4981,15 +5041,15 @@
         <v>74</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5012,13 +5072,13 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5069,7 +5129,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -5089,10 +5149,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5103,25 +5163,25 @@
         <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K39" t="s" s="2">
+      <c r="L39" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5172,13 +5232,13 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
@@ -5187,19 +5247,19 @@
         <v>74</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5218,16 +5278,16 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5265,19 +5325,19 @@
         <v>74</v>
       </c>
       <c r="AB40" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC40" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC40" t="s" s="2">
+      <c r="AD40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE40" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE40" t="s" s="2">
+      <c r="AF40" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5289,18 +5349,18 @@
         <v>74</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5323,7 +5383,7 @@
         <v>107</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>108</v>
@@ -5332,7 +5392,7 @@
         <v>109</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>110</v>
@@ -5396,18 +5456,18 @@
         <v>74</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5415,28 +5475,28 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K42" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L42" t="s" s="2">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5487,13 +5547,13 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>74</v>
@@ -5502,15 +5562,15 @@
         <v>74</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>74</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5518,28 +5578,28 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L43" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5590,13 +5650,13 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>74</v>
@@ -5605,15 +5665,15 @@
         <v>74</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>74</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5621,28 +5681,28 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L44" t="s" s="2">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5693,13 +5753,13 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>74</v>
@@ -5708,15 +5768,15 @@
         <v>74</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>74</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5724,28 +5784,28 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="G45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L45" t="s" s="2">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5796,13 +5856,13 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>74</v>
@@ -5811,15 +5871,15 @@
         <v>74</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5842,13 +5902,13 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5899,7 +5959,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -5919,10 +5979,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5933,25 +5993,25 @@
         <v>75</v>
       </c>
       <c r="G47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K47" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K47" t="s" s="2">
+      <c r="L47" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6002,13 +6062,13 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
@@ -6017,19 +6077,19 @@
         <v>74</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6048,16 +6108,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6095,19 +6155,19 @@
         <v>74</v>
       </c>
       <c r="AB48" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC48" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC48" t="s" s="2">
+      <c r="AD48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE48" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE48" t="s" s="2">
+      <c r="AF48" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -6119,18 +6179,18 @@
         <v>74</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6153,7 +6213,7 @@
         <v>107</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>108</v>
@@ -6162,7 +6222,7 @@
         <v>109</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>110</v>
@@ -6226,18 +6286,18 @@
         <v>74</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6248,7 +6308,7 @@
         <v>75</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6260,13 +6320,13 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6317,13 +6377,13 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>74</v>
@@ -6332,15 +6392,15 @@
         <v>74</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>74</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6351,7 +6411,7 @@
         <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -6363,13 +6423,13 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6420,13 +6480,13 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>74</v>
@@ -6435,15 +6495,15 @@
         <v>74</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>74</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6466,13 +6526,13 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6523,7 +6583,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -6543,10 +6603,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6554,10 +6614,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -6569,13 +6629,13 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6626,13 +6686,13 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
@@ -6646,10 +6706,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6660,7 +6720,7 @@
         <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
@@ -6672,13 +6732,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6729,13 +6789,13 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>74</v>
@@ -6749,10 +6809,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6775,13 +6835,13 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6832,7 +6892,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -6852,10 +6912,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6866,25 +6926,25 @@
         <v>75</v>
       </c>
       <c r="G56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K56" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K56" t="s" s="2">
+      <c r="L56" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6935,13 +6995,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>74</v>
@@ -6950,19 +7010,19 @@
         <v>74</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -6981,16 +7041,16 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7028,19 +7088,19 @@
         <v>74</v>
       </c>
       <c r="AB57" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC57" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC57" t="s" s="2">
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE57" t="s" s="2">
+      <c r="AF57" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7052,18 +7112,18 @@
         <v>74</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7086,7 +7146,7 @@
         <v>107</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>108</v>
@@ -7095,7 +7155,7 @@
         <v>109</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>110</v>
@@ -7159,18 +7219,18 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7193,13 +7253,13 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7250,7 +7310,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -7270,10 +7330,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7284,25 +7344,25 @@
         <v>75</v>
       </c>
       <c r="G60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K60" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K60" t="s" s="2">
+      <c r="L60" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7353,13 +7413,13 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>74</v>
@@ -7368,19 +7428,19 @@
         <v>74</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -7399,16 +7459,16 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7446,19 +7506,19 @@
         <v>74</v>
       </c>
       <c r="AB61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC61" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC61" t="s" s="2">
+      <c r="AD61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE61" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE61" t="s" s="2">
+      <c r="AF61" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -7470,18 +7530,18 @@
         <v>74</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7504,7 +7564,7 @@
         <v>107</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>108</v>
@@ -7513,7 +7573,7 @@
         <v>109</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>110</v>
@@ -7577,18 +7637,18 @@
         <v>74</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7611,13 +7671,13 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7668,7 +7728,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -7683,15 +7743,15 @@
         <v>74</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>74</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7699,10 +7759,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>74</v>
@@ -7714,13 +7774,13 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7771,13 +7831,13 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>74</v>
@@ -7791,10 +7851,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7817,13 +7877,13 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7874,7 +7934,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -7889,15 +7949,15 @@
         <v>81</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7908,25 +7968,25 @@
         <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K66" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K66" t="s" s="2">
+      <c r="L66" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -7977,13 +8037,13 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>74</v>
@@ -7992,19 +8052,19 @@
         <v>74</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -8023,16 +8083,16 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8070,19 +8130,19 @@
         <v>74</v>
       </c>
       <c r="AB67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC67" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC67" t="s" s="2">
+      <c r="AD67" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE67" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE67" t="s" s="2">
+      <c r="AF67" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
@@ -8094,18 +8154,18 @@
         <v>74</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8128,7 +8188,7 @@
         <v>107</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>108</v>
@@ -8137,7 +8197,7 @@
         <v>109</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>110</v>
@@ -8201,18 +8261,18 @@
         <v>74</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8235,13 +8295,13 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8265,7 +8325,7 @@
         <v>74</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="X69" t="s" s="2">
         <v>74</v>
@@ -8292,7 +8352,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -8312,10 +8372,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8323,10 +8383,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>74</v>
@@ -8338,13 +8398,13 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8395,13 +8455,13 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>74</v>
@@ -8415,10 +8475,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8429,7 +8489,7 @@
         <v>75</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>74</v>
@@ -8441,13 +8501,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8498,13 +8558,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8518,10 +8578,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8532,25 +8592,25 @@
         <v>75</v>
       </c>
       <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K72" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K72" t="s" s="2">
+      <c r="L72" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8601,13 +8661,13 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>74</v>
@@ -8616,19 +8676,19 @@
         <v>74</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -8647,16 +8707,16 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -8694,19 +8754,19 @@
         <v>74</v>
       </c>
       <c r="AB73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC73" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC73" t="s" s="2">
+      <c r="AD73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE73" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE73" t="s" s="2">
+      <c r="AF73" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -8718,18 +8778,18 @@
         <v>74</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8752,7 +8812,7 @@
         <v>107</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>108</v>
@@ -8761,7 +8821,7 @@
         <v>109</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>110</v>
@@ -8825,18 +8885,18 @@
         <v>74</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8847,25 +8907,25 @@
         <v>75</v>
       </c>
       <c r="G75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K75" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L75" t="s" s="2">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -8916,13 +8976,13 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>74</v>
@@ -8931,15 +8991,15 @@
         <v>74</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>74</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8950,25 +9010,25 @@
         <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K76" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L76" t="s" s="2">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9019,13 +9079,13 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>74</v>
@@ -9034,15 +9094,15 @@
         <v>74</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>74</v>
+        <v>247</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9065,13 +9125,13 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9122,7 +9182,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -9142,10 +9202,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9156,25 +9216,25 @@
         <v>75</v>
       </c>
       <c r="G78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K78" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K78" t="s" s="2">
+      <c r="L78" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9225,13 +9285,13 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
@@ -9240,19 +9300,19 @@
         <v>74</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -9271,16 +9331,16 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9318,19 +9378,19 @@
         <v>74</v>
       </c>
       <c r="AB79" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC79" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC79" t="s" s="2">
+      <c r="AD79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE79" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE79" t="s" s="2">
+      <c r="AF79" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -9342,18 +9402,18 @@
         <v>74</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9376,7 +9436,7 @@
         <v>107</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>108</v>
@@ -9385,7 +9445,7 @@
         <v>109</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O80" t="s" s="2">
         <v>110</v>
@@ -9449,18 +9509,18 @@
         <v>74</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9483,13 +9543,13 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9540,7 +9600,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
@@ -9560,10 +9620,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9586,13 +9646,13 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9643,7 +9703,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
@@ -9663,10 +9723,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9674,10 +9734,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>74</v>
@@ -9689,13 +9749,13 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9746,13 +9806,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -9766,10 +9826,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9780,7 +9840,7 @@
         <v>75</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>74</v>
@@ -9792,13 +9852,13 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9849,13 +9909,13 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>74</v>
@@ -9869,10 +9929,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9880,10 +9940,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -9895,13 +9955,13 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -9952,13 +10012,13 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
@@ -9972,10 +10032,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -9998,13 +10058,13 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10055,7 +10115,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
@@ -10075,10 +10135,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10101,13 +10161,13 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10158,7 +10218,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -10178,10 +10238,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10192,25 +10252,25 @@
         <v>75</v>
       </c>
       <c r="G88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K88" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K88" t="s" s="2">
+      <c r="L88" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10261,13 +10321,13 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>74</v>
@@ -10276,19 +10336,19 @@
         <v>74</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -10307,16 +10367,16 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10354,19 +10414,19 @@
         <v>74</v>
       </c>
       <c r="AB89" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC89" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="AC89" t="s" s="2">
+      <c r="AD89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE89" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AD89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE89" t="s" s="2">
+      <c r="AF89" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -10378,18 +10438,18 @@
         <v>74</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10412,7 +10472,7 @@
         <v>107</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>108</v>
@@ -10421,7 +10481,7 @@
         <v>109</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>110</v>
@@ -10485,18 +10545,18 @@
         <v>74</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10519,13 +10579,13 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10576,7 +10636,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -10591,7 +10651,7 @@
         <v>74</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>74</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
